--- a/nriss-patch-1/ig/StructureDefinition-fr-lm-patient-sujet-non-humain.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-lm-patient-sujet-non-humain.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Patient avec sujet non humain</t>
+    <t>Logical model - FR LM Patient avec sujet non humain</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/StructureDefinition-fr-lm-patient-sujet-non-humain.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-lm-patient-sujet-non-humain.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
